--- a/cotacoes/2026-09-04/PEDIDO_EPAN_04-09-2026.xlsx
+++ b/cotacoes/2026-09-04/PEDIDO_EPAN_04-09-2026.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P86"/>
+  <dimension ref="A1:P84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -942,51 +942,51 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>708096</t>
+          <t>719603</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>556121</v>
+        <v>584301</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7896658026850</t>
+          <t>4987188568729</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>BIOZINC KIDS 2MG SOLUCAO 75ML</t>
+          <t>BYE BYE FEVER CRIANCA 2 UNIDADES</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>BIOZINC KIDS 2MG FR 75ML</t>
+          <t>BYE BYE FEVER PARA CRIANCAS C/2UN(HSM)</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>30.35</v>
+        <v>9.58</v>
       </c>
       <c r="J8" s="4">
         <f>G8*I8</f>
         <v/>
       </c>
       <c r="K8" s="4" t="n">
-        <v>30.35</v>
+        <v>9.58</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>32.5566666666667</v>
+        <v>11.07</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>28.134</v>
+        <v>8.99</v>
       </c>
       <c r="N8" s="5">
         <f>K8/L8-1</f>
@@ -1002,59 +1002,59 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>719603</t>
+          <t>716050</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>584301</v>
+        <v>606351</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4987188568729</t>
+          <t>7896004780078</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>BYE BYE FEVER CRIANCA 2 UNIDADES</t>
+          <t>CREME CALADRYL POS SOL 28G</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>BYE BYE FEVER PARA CRIANCAS C/2UN(HSM)</t>
+          <t>CALADRYL POS SOL CR 28G</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>9.58</v>
+        <v>21.21</v>
       </c>
       <c r="J9" s="4">
         <f>G9*I9</f>
         <v/>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9.58</v>
+        <v>21.21</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>11.07</v>
+        <v>18.74</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>8.99</v>
+        <v>14.1583</v>
       </c>
       <c r="N9" s="5">
         <f>K9/L9-1</f>
         <v/>
       </c>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>ACIMA +13.2% (vs últ. compra)</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr"/>
@@ -1062,25 +1062,25 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>716050</t>
+          <t>705541</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>606351</v>
+        <v>539701</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7896004780078</t>
+          <t>7898414850891</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>CREME CALADRYL POS SOL 28G</t>
+          <t>CALCITRAN D3 30 COMPRIMIDOS</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>CALADRYL POS SOL CR 28G</t>
+          <t>CALCITRAN D3 CX 30 COMP</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
@@ -1093,20 +1093,20 @@
         <v>1</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>21.21</v>
+        <v>36.55</v>
       </c>
       <c r="J10" s="4">
         <f>G10*I10</f>
         <v/>
       </c>
       <c r="K10" s="4" t="n">
-        <v>21.21</v>
+        <v>36.55</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>18.74</v>
+        <v>36.48</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>14.1583</v>
+        <v>30.8</v>
       </c>
       <c r="N10" s="5">
         <f>K10/L10-1</f>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>ACIMA +13.2% (vs últ. compra)</t>
+          <t>ACIMA +0.2% (vs últ. compra)</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr"/>
@@ -1122,59 +1122,59 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>705541</t>
+          <t>100664</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>539701</v>
+        <v>210221</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7898414850891</t>
+          <t>7896261013490</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>CALCITRAN D3 30 COMPRIMIDOS</t>
+          <t>CATAFLAM 50MG C/10 DRAGEAS</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>CALCITRAN D3 CX 30 COMP</t>
+          <t>CATAFLAM 50MG CX 10 DRG</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>36.55</v>
+        <v>17.03</v>
       </c>
       <c r="J11" s="4">
         <f>G11*I11</f>
         <v/>
       </c>
       <c r="K11" s="4" t="n">
-        <v>36.55</v>
+        <v>17.03</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>36.48</v>
+        <v>17.03</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>30.8</v>
+        <v>16.38</v>
       </c>
       <c r="N11" s="5">
         <f>K11/L11-1</f>
         <v/>
       </c>
-      <c r="O11" s="7" t="inlineStr">
-        <is>
-          <t>ACIMA +0.2% (vs últ. compra)</t>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr"/>
@@ -1182,51 +1182,51 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>100664</t>
+          <t>722182</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>210221</v>
+        <v>653981</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7896261013490</t>
+          <t>7500435231510</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>CATAFLAM 50MG C/10 DRAGEAS</t>
+          <t>CEBION SABOR LARANJA SEM AÇUCAR 1G C/10 COMPRIMIDOS EFERVESCENTES</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>CATAFLAM 50MG CX 10 DRG</t>
+          <t>CEBION EFV 1G C/10 COMP-DEMAIS PROD</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>17.03</v>
+        <v>12.03</v>
       </c>
       <c r="J12" s="4">
         <f>G12*I12</f>
         <v/>
       </c>
       <c r="K12" s="4" t="n">
-        <v>17.03</v>
+        <v>12.03</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>17.03</v>
+        <v>14.32</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>16.38</v>
+        <v>10.775</v>
       </c>
       <c r="N12" s="5">
         <f>K12/L12-1</f>
@@ -1242,25 +1242,25 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>722182</t>
+          <t>721243</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>653981</v>
+        <v>636021</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7500435231510</t>
+          <t>7899706192057</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>CEBION SABOR LARANJA SEM AÇUCAR 1G C/10 COMPRIMIDOS EFERVESCENTES</t>
+          <t>CERAVE CREME REPARADOR PARA OLHOS 15G</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>CEBION EFV 1G C/10 COMP-DEMAIS PROD</t>
+          <t>CERAVE CR OLHOS 15G</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
@@ -1273,20 +1273,20 @@
         <v>1</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>12.03</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="J13" s="4">
         <f>G13*I13</f>
         <v/>
       </c>
       <c r="K13" s="4" t="n">
-        <v>12.03</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>14.32</v>
+        <v>87.33</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>10.775</v>
+        <v>87.33</v>
       </c>
       <c r="N13" s="5">
         <f>K13/L13-1</f>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>OK (≤ menor hist.)</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr"/>
@@ -1302,51 +1302,51 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>721243</t>
+          <t>722207</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>636021</v>
+        <v>653331</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7899706192057</t>
+          <t>7908615086309</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>CERAVE CREME REPARADOR PARA OLHOS 15G</t>
+          <t>LOCAO HIDRATANTE SEM PERFUME CERAVE FRASCO 340ML</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>CERAVE CR OLHOS 15G</t>
+          <t>CERAVE LOCAO HIDRATANTE 340ML-DEMAIS PROD</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>78.95999999999999</v>
+        <v>69.48</v>
       </c>
       <c r="J14" s="4">
         <f>G14*I14</f>
         <v/>
       </c>
       <c r="K14" s="4" t="n">
+        <v>69.48</v>
+      </c>
+      <c r="L14" s="4" t="n">
         <v>78.95999999999999</v>
       </c>
-      <c r="L14" s="4" t="n">
-        <v>87.33</v>
-      </c>
       <c r="M14" s="4" t="n">
-        <v>87.33</v>
+        <v>66.325</v>
       </c>
       <c r="N14" s="5">
         <f>K14/L14-1</f>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr"/>
@@ -1362,51 +1362,51 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>722207</t>
+          <t>720235</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>653331</v>
+        <v>624291</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7908615086309</t>
+          <t>7899706211178</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>LOCAO HIDRATANTE SEM PERFUME CERAVE FRASCO 340ML</t>
+          <t>GEL DE LIMPEZA CERAVE SA RENOVADOR SEM PERFUME COM 150G</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>CERAVE LOCAO HIDRATANTE 340ML-DEMAIS PROD</t>
+          <t>CERAVE SA GEL DE LIMPEZA RENOVA 150G</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>69.48</v>
+        <v>53.04</v>
       </c>
       <c r="J15" s="4">
         <f>G15*I15</f>
         <v/>
       </c>
       <c r="K15" s="4" t="n">
-        <v>69.48</v>
+        <v>53.04</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>78.95999999999999</v>
+        <v>65.59</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>66.325</v>
+        <v>65.59</v>
       </c>
       <c r="N15" s="5">
         <f>K15/L15-1</f>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>OK (≤ menor hist.)</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr"/>
@@ -1422,51 +1422,51 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>720235</t>
+          <t>100712</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>624291</v>
+        <v>654251</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>7899706211178</t>
+          <t>7897337716215</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>GEL DE LIMPEZA CERAVE SA RENOVADOR SEM PERFUME COM 150G</t>
+          <t>CERAZETTE C/28 COMPRIMIDOS</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>CERAVE SA GEL DE LIMPEZA RENOVA 150G</t>
+          <t>CERAZETTE 75MCG 28CPR</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>53.04</v>
+        <v>37.81</v>
       </c>
       <c r="J16" s="4">
         <f>G16*I16</f>
         <v/>
       </c>
       <c r="K16" s="4" t="n">
-        <v>53.04</v>
+        <v>37.81</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>65.59</v>
+        <v>37.81</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>65.59</v>
+        <v>35.07</v>
       </c>
       <c r="N16" s="5">
         <f>K16/L16-1</f>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="O16" s="6" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr"/>
@@ -1482,51 +1482,51 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>100712</t>
+          <t>700549</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>654251</v>
+        <v>383</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7897337716215</t>
+          <t>7897930777743</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>CERAZETTE C/28 COMPRIMIDOS</t>
+          <t>CETAPHIL LOCAO HIDRATANTE CORPO E ROSTO 473ML</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>CERAZETTE 75MCG 28CPR</t>
+          <t>CETAPHIL LOC HIDRATANTE 473ML</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>37.81</v>
+        <v>85.77</v>
       </c>
       <c r="J17" s="4">
         <f>G17*I17</f>
         <v/>
       </c>
       <c r="K17" s="4" t="n">
-        <v>37.81</v>
+        <v>85.77</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>37.81</v>
+        <v>102.75</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>35.07</v>
+        <v>85.77</v>
       </c>
       <c r="N17" s="5">
         <f>K17/L17-1</f>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>OK (≤ menor hist.)</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr"/>
@@ -1542,51 +1542,51 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>700549</t>
+          <t>708526</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>383</v>
+        <v>963</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7897930777743</t>
+          <t>7908615000169</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>CETAPHIL LOCAO HIDRATANTE CORPO E ROSTO 473ML</t>
+          <t>CICAPLAST BAUME B5 TUBO 20ML</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>CETAPHIL LOC HIDRATANTE 473ML</t>
+          <t>CICAPLAST B5 PLUS 20ML-DEMAIS PROD</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>85.77</v>
+        <v>39.44</v>
       </c>
       <c r="J18" s="4">
         <f>G18*I18</f>
         <v/>
       </c>
       <c r="K18" s="4" t="n">
-        <v>85.77</v>
+        <v>39.44</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>102.75</v>
+        <v>44.74</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>85.77</v>
+        <v>35.88</v>
       </c>
       <c r="N18" s="5">
         <f>K18/L18-1</f>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="O18" s="6" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr"/>
@@ -1602,51 +1602,51 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>708526</t>
+          <t>700583</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>963</v>
+        <v>594261</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7908615000169</t>
+          <t>7898949409625</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>CICAPLAST BAUME B5 TUBO 20ML</t>
+          <t>CICATRICURE GEL 30G</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>CICAPLAST B5 PLUS 20ML-DEMAIS PROD</t>
+          <t>CICATRICURE GEL CICATRIZ/ESTRIAS 30G</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>39.44</v>
+        <v>23.82</v>
       </c>
       <c r="J19" s="4">
         <f>G19*I19</f>
         <v/>
       </c>
       <c r="K19" s="4" t="n">
-        <v>39.44</v>
+        <v>23.82</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>44.74</v>
+        <v>24.85</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>35.88</v>
+        <v>16.73</v>
       </c>
       <c r="N19" s="5">
         <f>K19/L19-1</f>
@@ -1662,25 +1662,25 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>700583</t>
+          <t>400336</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>594261</v>
+        <v>161441</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>7898949409625</t>
+          <t>7896548113479</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>CICATRICURE GEL 30G</t>
+          <t>CLARIL SOLUCAO OFTALMICA 15ML</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>CICATRICURE GEL CICATRIZ/ESTRIAS 30G</t>
+          <t>CLARIL 0,25+3MG SOL FR OFT GTS 15ML</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
@@ -1693,20 +1693,20 @@
         <v>1</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>23.82</v>
+        <v>21.37</v>
       </c>
       <c r="J20" s="4">
         <f>G20*I20</f>
         <v/>
       </c>
       <c r="K20" s="4" t="n">
-        <v>23.82</v>
+        <v>21.37</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>24.85</v>
+        <v>21.37</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>16.73</v>
+        <v>18.9119</v>
       </c>
       <c r="N20" s="5">
         <f>K20/L20-1</f>
@@ -1722,59 +1722,59 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>400336</t>
+          <t>115680</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>161441</v>
+        <v>674291</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7896548113479</t>
+          <t>7896637035736</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>CLARIL SOLUCAO OFTALMICA 15ML</t>
+          <t>COBI-12 1000MCG C/30 COMPRIMIDOS SUBLINGUAIS</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>CLARIL 0,25+3MG SOL FR OFT GTS 15ML</t>
+          <t>COBI-12 1000MCG C/30 COMP SUBL-OUTROS</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>21.37</v>
+        <v>22.81</v>
       </c>
       <c r="J21" s="4">
         <f>G21*I21</f>
         <v/>
       </c>
       <c r="K21" s="4" t="n">
-        <v>21.37</v>
+        <v>22.81</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>21.37</v>
+        <v>22.805</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>18.9119</v>
+        <v>18.8279</v>
       </c>
       <c r="N21" s="5">
         <f>K21/L21-1</f>
         <v/>
       </c>
-      <c r="O21" s="6" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>ACIMA +0.0% (vs últ. compra)</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr"/>
@@ -1782,59 +1782,59 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>115680</t>
+          <t>400349</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>674291</v>
+        <v>114941</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>7896637035736</t>
+          <t>7899824400928</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>COBI-12 1000MCG C/30 COMPRIMIDOS SUBLINGUAIS</t>
+          <t>COLPIST MT CREME VAGINAL 40G C/10 APLICADORES</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>COBI-12 1000MCG C/30 COMP SUBL-OUTROS</t>
+          <t>COLPIST MT 62,5+1,25MG/G+25000UI/G CREM BG 40G+10APLIC</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>22.81</v>
+        <v>35.98</v>
       </c>
       <c r="J22" s="4">
         <f>G22*I22</f>
         <v/>
       </c>
       <c r="K22" s="4" t="n">
-        <v>22.81</v>
+        <v>35.98</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>22.805</v>
+        <v>45.99</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>18.8279</v>
+        <v>35.9767</v>
       </c>
       <c r="N22" s="5">
         <f>K22/L22-1</f>
         <v/>
       </c>
-      <c r="O22" s="7" t="inlineStr">
-        <is>
-          <t>ACIMA +0.0% (vs últ. compra)</t>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr"/>
@@ -1842,25 +1842,25 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>400349</t>
+          <t>710474</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>114941</v>
+        <v>556501</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>7899824400928</t>
+          <t>42277217</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>COLPIST MT CREME VAGINAL 40G C/10 APLICADORES</t>
+          <t>CREME HIDRATANTE NIVEA LATA 29G</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>COLPIST MT 62,5+1,25MG/G+25000UI/G CREM BG 40G+10APLIC</t>
+          <t>CR NIVEA 29G</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
@@ -1873,20 +1873,20 @@
         <v>2</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>35.98</v>
+        <v>11.57</v>
       </c>
       <c r="J23" s="4">
         <f>G23*I23</f>
         <v/>
       </c>
       <c r="K23" s="4" t="n">
-        <v>35.98</v>
+        <v>11.57</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>45.99</v>
+        <v>14.24</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>35.9767</v>
+        <v>8.833299999999999</v>
       </c>
       <c r="N23" s="5">
         <f>K23/L23-1</f>
@@ -1902,51 +1902,51 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>710474</t>
+          <t>101046</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>556501</v>
+        <v>6581</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>42277217</t>
+          <t>7891268101799</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>CREME HIDRATANTE NIVEA LATA 29G</t>
+          <t>DEPO PROVERA 150MG C/1 AMPOLA 1ML</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>CR NIVEA 29G</t>
+          <t>DEPO PROVERA 150MG SUS INJ 1FA X 1ML</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>11.57</v>
+        <v>36.87</v>
       </c>
       <c r="J24" s="4">
         <f>G24*I24</f>
         <v/>
       </c>
       <c r="K24" s="4" t="n">
-        <v>11.57</v>
+        <v>36.87</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>14.24</v>
+        <v>36.87</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>8.833299999999999</v>
+        <v>33.56</v>
       </c>
       <c r="N24" s="5">
         <f>K24/L24-1</f>
@@ -1962,25 +1962,25 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>101046</t>
+          <t>705256</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>6581</v>
+        <v>603851</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>7891268101799</t>
+          <t>7896004790657</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>DEPO PROVERA 150MG C/1 AMPOLA 1ML</t>
+          <t>DERMACYD FEMINA BREEZE LIQUIDO 200ML</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>DEPO PROVERA 150MG SUS INJ 1FA X 1ML</t>
+          <t>DERMACYD SAB LIQ BREE 200ML</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
@@ -1993,28 +1993,28 @@
         <v>3</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>36.87</v>
+        <v>19.95</v>
       </c>
       <c r="J25" s="4">
         <f>G25*I25</f>
         <v/>
       </c>
       <c r="K25" s="4" t="n">
-        <v>36.87</v>
+        <v>19.95</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>36.87</v>
+        <v>18.92</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>33.56</v>
+        <v>17.14</v>
       </c>
       <c r="N25" s="5">
         <f>K25/L25-1</f>
         <v/>
       </c>
-      <c r="O25" s="6" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>ACIMA +5.4% (vs últ. compra)</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr"/>
@@ -2022,59 +2022,59 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>705256</t>
+          <t>708855</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>603851</v>
+        <v>623211</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>7896004790657</t>
+          <t>7899706126335</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>DERMACYD FEMINA BREEZE LIQUIDO 200ML</t>
+          <t>AGUA MICELAR SOLUCAO DE LIMPEZA 5 EM 1 LOREAL PARIS 200ML</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>DERMACYD SAB LIQ BREE 200ML</t>
+          <t>DERMO EXP AGUA MICELAR 200ML</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>19.95</v>
+        <v>20.36</v>
       </c>
       <c r="J26" s="4">
         <f>G26*I26</f>
         <v/>
       </c>
       <c r="K26" s="4" t="n">
-        <v>19.95</v>
+        <v>20.36</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>18.92</v>
+        <v>21.97</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>17.14</v>
+        <v>18.7783</v>
       </c>
       <c r="N26" s="5">
         <f>K26/L26-1</f>
         <v/>
       </c>
-      <c r="O26" s="7" t="inlineStr">
-        <is>
-          <t>ACIMA +5.4% (vs últ. compra)</t>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr"/>
@@ -2082,51 +2082,51 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>708855</t>
+          <t>101107</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>623211</v>
+        <v>539561</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>7899706126335</t>
+          <t>7891106913966</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>AGUA MICELAR SOLUCAO DE LIMPEZA 5 EM 1 LOREAL PARIS 200ML</t>
+          <t>DIANE 35 C/21 DRAGEAS</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>DERMO EXP AGUA MICELAR 200ML</t>
+          <t>DIANE 35 2+0,035MG CX 21 DRG</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>20.36</v>
+        <v>32.08</v>
       </c>
       <c r="J27" s="4">
         <f>G27*I27</f>
         <v/>
       </c>
       <c r="K27" s="4" t="n">
-        <v>20.36</v>
+        <v>32.08</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>21.97</v>
+        <v>32.08</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>18.7783</v>
+        <v>27.875</v>
       </c>
       <c r="N27" s="5">
         <f>K27/L27-1</f>
@@ -2142,51 +2142,51 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>101107</t>
+          <t>105283</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>539561</v>
+        <v>309701</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>7891106913966</t>
+          <t>7896255767149</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>DIANE 35 C/21 DRAGEAS</t>
+          <t>DUPHALAC 667MG XAROPE 200ML</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>DIANE 35 2+0,035MG CX 21 DRG</t>
+          <t>DUPHALAC 667MG/ML XPE FR X 200ML</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>32.08</v>
+        <v>45.81</v>
       </c>
       <c r="J28" s="4">
         <f>G28*I28</f>
         <v/>
       </c>
       <c r="K28" s="4" t="n">
-        <v>32.08</v>
+        <v>45.81</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>32.08</v>
+        <v>45.815</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>27.875</v>
+        <v>42.55</v>
       </c>
       <c r="N28" s="5">
         <f>K28/L28-1</f>
@@ -2202,51 +2202,51 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>105283</t>
+          <t>101509</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>309701</v>
+        <v>240601</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>7896255767149</t>
+          <t>7896637023344</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>DUPHALAC 667MG XAROPE 200ML</t>
+          <t>FLANCOX 400MG C/10 COMPRIMIDOS</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>DUPHALAC 667MG/ML XPE FR X 200ML</t>
+          <t>FLANCOX 400MG CX 10 COMP REV</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>45.81</v>
+        <v>21.83</v>
       </c>
       <c r="J29" s="4">
         <f>G29*I29</f>
         <v/>
       </c>
       <c r="K29" s="4" t="n">
-        <v>45.81</v>
+        <v>21.83</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>45.815</v>
+        <v>21.8385714285714</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>42.55</v>
+        <v>20.78</v>
       </c>
       <c r="N29" s="5">
         <f>K29/L29-1</f>
@@ -2262,51 +2262,51 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>101509</t>
+          <t>107760</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>240601</v>
+        <v>240241</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>7896637023344</t>
+          <t>7896637023238</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>FLANCOX 400MG C/10 COMPRIMIDOS</t>
+          <t>FLANCOX 500MG C/14 COMPRIMIDOS REV</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>FLANCOX 400MG CX 10 COMP REV</t>
+          <t>FLANCOX 500MG CX 14 COMP REV</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>21.83</v>
+        <v>27.92</v>
       </c>
       <c r="J30" s="4">
         <f>G30*I30</f>
         <v/>
       </c>
       <c r="K30" s="4" t="n">
-        <v>21.83</v>
+        <v>27.92</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>21.8385714285714</v>
+        <v>27.925</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>20.78</v>
+        <v>25.425</v>
       </c>
       <c r="N30" s="5">
         <f>K30/L30-1</f>
@@ -2322,51 +2322,51 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>107760</t>
+          <t>400575</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>240241</v>
+        <v>589611</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>7896637023238</t>
+          <t>7898040329570</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>FLANCOX 500MG C/14 COMPRIMIDOS REV</t>
+          <t>FLORATIL 200MG PEDIATRICO C/4 ENVELOPES</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>FLANCOX 500MG CX 14 COMP REV</t>
+          <t>FLORATIL 200MG/G PO OR 4 ENV X 1G</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>27.92</v>
+        <v>28</v>
       </c>
       <c r="J31" s="4">
         <f>G31*I31</f>
         <v/>
       </c>
       <c r="K31" s="4" t="n">
-        <v>27.92</v>
+        <v>28</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>27.925</v>
+        <v>28</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>25.425</v>
+        <v>7.05</v>
       </c>
       <c r="N31" s="5">
         <f>K31/L31-1</f>
@@ -2382,51 +2382,51 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>400575</t>
+          <t>404987</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>589611</v>
+        <v>622951</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>7898040329570</t>
+          <t>7898040329679</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>FLORATIL 200MG PEDIATRICO C/4 ENVELOPES</t>
+          <t>PROBIOTICO FLORATIL AT 250MG COM 6 CAPSULAS</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>FLORATIL 200MG/G PO OR 4 ENV X 1G</t>
+          <t>FLORATIL 250MG BL 6 CAP</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>28</v>
+        <v>36.53</v>
       </c>
       <c r="J32" s="4">
         <f>G32*I32</f>
         <v/>
       </c>
       <c r="K32" s="4" t="n">
-        <v>28</v>
+        <v>36.53</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>28</v>
+        <v>38.6416666666667</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>7.05</v>
+        <v>31.31</v>
       </c>
       <c r="N32" s="5">
         <f>K32/L32-1</f>
@@ -2442,25 +2442,25 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>404987</t>
+          <t>405483</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>622951</v>
+        <v>635741</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>7898040329679</t>
+          <t>7891106916059</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>PROBIOTICO FLORATIL AT 250MG COM 6 CAPSULAS</t>
+          <t>GINO CANESTEN 500MG 1COMP VAGINAL + 1 APLICADOR</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>FLORATIL 250MG BL 6 CAP</t>
+          <t>GINO CANESTEN 1 500MG 1COMP+APL-REFERENCIA</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
@@ -2473,20 +2473,20 @@
         <v>3</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>36.53</v>
+        <v>72.45</v>
       </c>
       <c r="J33" s="4">
         <f>G33*I33</f>
         <v/>
       </c>
       <c r="K33" s="4" t="n">
-        <v>36.53</v>
+        <v>72.45</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>38.6416666666667</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>31.31</v>
+        <v>68.87</v>
       </c>
       <c r="N33" s="5">
         <f>K33/L33-1</f>
@@ -2502,51 +2502,51 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>405483</t>
+          <t>405167</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>635741</v>
+        <v>639851</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>7891106916059</t>
+          <t>7899095200586</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>GINO CANESTEN 500MG 1COMP VAGINAL + 1 APLICADOR</t>
+          <t>HILUROPT HIALURONATO DE SODIO 0,15% SOLUÇAO OFTALMICA 10ML</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>GINO CANESTEN 1 500MG 1COMP+APL-REFERENCIA</t>
+          <t>HILUROPT 1,5MG/ML SOL OFT FR GOT X 10ML</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>72.45</v>
+        <v>36.09</v>
       </c>
       <c r="J34" s="4">
         <f>G34*I34</f>
         <v/>
       </c>
       <c r="K34" s="4" t="n">
-        <v>72.45</v>
+        <v>36.09</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>80.51000000000001</v>
+        <v>39.465</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>68.87</v>
+        <v>33.63</v>
       </c>
       <c r="N34" s="5">
         <f>K34/L34-1</f>
@@ -2562,51 +2562,47 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>405167</t>
+          <t>714665</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>639851</v>
+        <v>554181</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>7899095200586</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>HILUROPT HIALURONATO DE SODIO 0,15% SOLUÇAO OFTALMICA 10ML</t>
-        </is>
-      </c>
+          <t>7891010249953</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>HILUROPT 1,5MG/ML SOL OFT FR GOT X 10ML</t>
+          <t>HIPOGLOS AMENDOAS 40G</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>36.09</v>
+        <v>20.67</v>
       </c>
       <c r="J35" s="4">
         <f>G35*I35</f>
         <v/>
       </c>
       <c r="K35" s="4" t="n">
-        <v>36.09</v>
+        <v>20.67</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>39.465</v>
+        <v>22.94</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>33.63</v>
+        <v>19.3367</v>
       </c>
       <c r="N35" s="5">
         <f>K35/L35-1</f>
@@ -2622,47 +2618,51 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>714665</t>
+          <t>721531</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>554181</v>
+        <v>621551</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>7891010249953</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr"/>
+          <t>7891010255763</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>HIPOGLOS POM ORIGINAL 40G</t>
+        </is>
+      </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>HIPOGLOS AMENDOAS 40G</t>
+          <t>HIPOGLOS ORIGINAL 40G</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>20.67</v>
+        <v>19.49</v>
       </c>
       <c r="J36" s="4">
         <f>G36*I36</f>
         <v/>
       </c>
       <c r="K36" s="4" t="n">
-        <v>20.67</v>
+        <v>19.49</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>22.94</v>
+        <v>21.3575</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>19.3367</v>
+        <v>18.405</v>
       </c>
       <c r="N36" s="5">
         <f>K36/L36-1</f>
@@ -2678,51 +2678,51 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>721531</t>
+          <t>402291</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>621551</v>
+        <v>406241</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>7891010255763</t>
+          <t>7897411601505</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>HIPOGLOS POM ORIGINAL 40G</t>
+          <t>HIRUDOID 300MG GEL 40G</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>HIPOGLOS ORIGINAL 40G</t>
+          <t>HIRUDOID 3MG/G GEL BG X 40G</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>19.49</v>
+        <v>32.92</v>
       </c>
       <c r="J37" s="4">
         <f>G37*I37</f>
         <v/>
       </c>
       <c r="K37" s="4" t="n">
-        <v>19.49</v>
+        <v>32.92</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>21.3575</v>
+        <v>32.92</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>18.405</v>
+        <v>28.79</v>
       </c>
       <c r="N37" s="5">
         <f>K37/L37-1</f>
@@ -2738,25 +2738,25 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>402291</t>
+          <t>402294</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>406241</v>
+        <v>406261</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>7897411601505</t>
+          <t>7897411601567</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>HIRUDOID 300MG GEL 40G</t>
+          <t>HIRUDOID 500MG POMADA 40G</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>HIRUDOID 3MG/G GEL BG X 40G</t>
+          <t>HIRUDOID 5MG/G POM BG X 40G</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
@@ -2769,20 +2769,20 @@
         <v>1</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>32.92</v>
+        <v>36.05</v>
       </c>
       <c r="J38" s="4">
         <f>G38*I38</f>
         <v/>
       </c>
       <c r="K38" s="4" t="n">
-        <v>32.92</v>
+        <v>36.05</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>32.92</v>
+        <v>36.05</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>28.79</v>
+        <v>31.52</v>
       </c>
       <c r="N38" s="5">
         <f>K38/L38-1</f>
@@ -2798,51 +2798,51 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>402294</t>
+          <t>718482</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>406261</v>
+        <v>594891</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>7897411601567</t>
+          <t>7898639690708</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>HIRUDOID 500MG POMADA 40G</t>
+          <t>G TECH INALADOR E NEBULIZADOR ULTRASSONICO NEBDESK 2</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>HIRUDOID 5MG/G POM BG X 40G</t>
+          <t>INALADOR NEBULIZADOR ULTRANEB DESK2</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>36.05</v>
+        <v>117.53</v>
       </c>
       <c r="J39" s="4">
         <f>G39*I39</f>
         <v/>
       </c>
       <c r="K39" s="4" t="n">
-        <v>36.05</v>
+        <v>117.53</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>36.05</v>
+        <v>130.26</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>31.52</v>
+        <v>130.26</v>
       </c>
       <c r="N39" s="5">
         <f>K39/L39-1</f>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="O39" s="6" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>OK (≤ menor hist.)</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr"/>
@@ -2858,51 +2858,51 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>718482</t>
+          <t>101918</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>594891</v>
+        <v>400881</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>7898639690708</t>
+          <t>7896641804380</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>G TECH INALADOR E NEBULIZADOR ULTRASSONICO NEBDESK 2</t>
+          <t>KALOBA GOTAS 20ML</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>INALADOR NEBULIZADOR ULTRANEB DESK2</t>
+          <t>KALOBA 825MG/ML SOL ORAL FR 20ML</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>117.53</v>
+        <v>77.37</v>
       </c>
       <c r="J40" s="4">
         <f>G40*I40</f>
         <v/>
       </c>
       <c r="K40" s="4" t="n">
-        <v>117.53</v>
+        <v>77.37</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>130.26</v>
+        <v>77.37</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>130.26</v>
+        <v>71.405</v>
       </c>
       <c r="N40" s="5">
         <f>K40/L40-1</f>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O40" s="6" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr"/>
@@ -2918,51 +2918,51 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>101918</t>
+          <t>101961</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>400881</v>
+        <v>129021</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>7896641804380</t>
+          <t>7896637028523</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>KALOBA GOTAS 20ML</t>
+          <t>LABIRIN 24MG C/30 COMPRIMIDOS</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>KALOBA 825MG/ML SOL ORAL FR 20ML</t>
+          <t>LABIRIN 24MG CX 30 COMP</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>77.37</v>
+        <v>19.44</v>
       </c>
       <c r="J41" s="4">
         <f>G41*I41</f>
         <v/>
       </c>
       <c r="K41" s="4" t="n">
-        <v>77.37</v>
+        <v>19.44</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>77.37</v>
+        <v>19.44</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>71.405</v>
+        <v>16.2667</v>
       </c>
       <c r="N41" s="5">
         <f>K41/L41-1</f>
@@ -2978,51 +2978,51 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>101961</t>
+          <t>115961</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>129021</v>
+        <v>671941</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>7896637028523</t>
+          <t>7891317040949</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>LABIRIN 24MG C/30 COMPRIMIDOS</t>
+          <t>LARC 600MG C/14 COMPRIMIDOS REVESTIDOS</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>LABIRIN 24MG CX 30 COMP</t>
+          <t>LARC 600MG C/14 COMP REV-SIMILAR</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>19.44</v>
+        <v>37.81</v>
       </c>
       <c r="J42" s="4">
         <f>G42*I42</f>
         <v/>
       </c>
       <c r="K42" s="4" t="n">
-        <v>19.44</v>
+        <v>37.81</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>19.44</v>
+        <v>43.96</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>16.2667</v>
+        <v>37.81</v>
       </c>
       <c r="N42" s="5">
         <f>K42/L42-1</f>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="O42" s="6" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>OK (≤ menor hist.)</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr"/>
@@ -3038,51 +3038,51 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>115961</t>
+          <t>400763</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>671941</v>
+        <v>539621</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>7891317040949</t>
+          <t>7895858015688</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>LARC 600MG C/14 COMPRIMIDOS REVESTIDOS</t>
+          <t>LEITE MAGNESIA PHILLIPS 120ML</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>LARC 600MG C/14 COMP REV-SIMILAR</t>
+          <t>LEITE MAGNESIA PHIL C/120ML</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>37.81</v>
+        <v>13.74</v>
       </c>
       <c r="J43" s="4">
         <f>G43*I43</f>
         <v/>
       </c>
       <c r="K43" s="4" t="n">
-        <v>37.81</v>
+        <v>13.74</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>43.96</v>
+        <v>16.875</v>
       </c>
       <c r="M43" s="4" t="n">
-        <v>37.81</v>
+        <v>8.1403</v>
       </c>
       <c r="N43" s="5">
         <f>K43/L43-1</f>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="O43" s="6" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr"/>
@@ -3098,51 +3098,51 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>400763</t>
+          <t>400764</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>539621</v>
+        <v>560961</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>7895858015688</t>
+          <t>7895858015695</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>LEITE MAGNESIA PHILLIPS 120ML</t>
+          <t>LEITE MAGNESIA PHILLIPS 350ML</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>LEITE MAGNESIA PHIL C/120ML</t>
+          <t>LEITE MAGNESIA PHILL 350ML</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>13.74</v>
+        <v>22.18</v>
       </c>
       <c r="J44" s="4">
         <f>G44*I44</f>
         <v/>
       </c>
       <c r="K44" s="4" t="n">
-        <v>13.74</v>
+        <v>22.18</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>16.875</v>
+        <v>27.2466666666667</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>8.1403</v>
+        <v>13.1507</v>
       </c>
       <c r="N44" s="5">
         <f>K44/L44-1</f>
@@ -3158,51 +3158,51 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>400764</t>
+          <t>102202</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>560961</v>
+        <v>206681</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>7895858015695</t>
+          <t>7896548111727</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>LEITE MAGNESIA PHILLIPS 350ML</t>
+          <t>MAXIDEX SOLUCAO OFTALMICA 5ML</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>LEITE MAGNESIA PHILL 350ML</t>
+          <t>MAXIDEX 1MG/ML SUS OFT FR GTS 5ML</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>22.18</v>
+        <v>8.23</v>
       </c>
       <c r="J45" s="4">
         <f>G45*I45</f>
         <v/>
       </c>
       <c r="K45" s="4" t="n">
-        <v>22.18</v>
+        <v>8.23</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>27.2466666666667</v>
+        <v>8.23</v>
       </c>
       <c r="M45" s="4" t="n">
-        <v>13.1507</v>
+        <v>7.8167</v>
       </c>
       <c r="N45" s="5">
         <f>K45/L45-1</f>
@@ -3218,51 +3218,47 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>102202</t>
+          <t>717171</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>206681</v>
+        <v>3223</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>7896548111727</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>MAXIDEX SOLUCAO OFTALMICA 5ML</t>
-        </is>
-      </c>
+          <t>7896023708626</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>MAXIDEX 1MG/ML SUS OFT FR GTS 5ML</t>
+          <t>MELAGRIAO SPRAY 30ML EXTRA FORTE</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>8.23</v>
+        <v>18.02</v>
       </c>
       <c r="J46" s="4">
         <f>G46*I46</f>
         <v/>
       </c>
       <c r="K46" s="4" t="n">
-        <v>8.23</v>
+        <v>18.02</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>8.23</v>
+        <v>21.72</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>7.8167</v>
+        <v>17.18</v>
       </c>
       <c r="N46" s="5">
         <f>K46/L46-1</f>
@@ -3278,47 +3274,51 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>717171</t>
+          <t>114887</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>3223</v>
+        <v>663861</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>7896023708626</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr"/>
+          <t>7891106916233</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>MESIGYNA 50+5MG/ML C/1 SERINGA PREENCHIDA + AGULHA</t>
+        </is>
+      </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>MELAGRIAO SPRAY 30ML EXTRA FORTE</t>
+          <t>MESIGYNA 50+5MG/ML C/1 SER PR+AG-REFERENCIA</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>18.02</v>
+        <v>35.54</v>
       </c>
       <c r="J47" s="4">
         <f>G47*I47</f>
         <v/>
       </c>
       <c r="K47" s="4" t="n">
-        <v>18.02</v>
+        <v>35.54</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>21.72</v>
+        <v>35.54</v>
       </c>
       <c r="M47" s="4" t="n">
-        <v>17.18</v>
+        <v>29.545</v>
       </c>
       <c r="N47" s="5">
         <f>K47/L47-1</f>
@@ -3334,51 +3334,51 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>114887</t>
+          <t>102323</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>663861</v>
+        <v>133581</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>7891106916233</t>
+          <t>7896637023665</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>MESIGYNA 50+5MG/ML C/1 SERINGA PREENCHIDA + AGULHA</t>
+          <t>MIOSAN 10MG C/10 COMPRIMIDOS</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>MESIGYNA 50+5MG/ML C/1 SER PR+AG-REFERENCIA</t>
+          <t>MIOSAN 10MG CX 10 COMP REV</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>35.54</v>
+        <v>12.44</v>
       </c>
       <c r="J48" s="4">
         <f>G48*I48</f>
         <v/>
       </c>
       <c r="K48" s="4" t="n">
-        <v>35.54</v>
+        <v>12.44</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>35.54</v>
+        <v>12.4416666666667</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>29.545</v>
+        <v>9.375</v>
       </c>
       <c r="N48" s="5">
         <f>K48/L48-1</f>
@@ -3394,25 +3394,25 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>102323</t>
+          <t>102352</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>133581</v>
+        <v>256161</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>7896637023665</t>
+          <t>7898074614178</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>MIOSAN 10MG C/10 COMPRIMIDOS</t>
+          <t>MONURIL C/1 ENVELOPES 8G</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>MIOSAN 10MG CX 10 COMP REV</t>
+          <t>MONURIL 5,631G GRAN ENV 8G</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
@@ -3425,20 +3425,20 @@
         <v>1</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>12.44</v>
+        <v>52.59</v>
       </c>
       <c r="J49" s="4">
         <f>G49*I49</f>
         <v/>
       </c>
       <c r="K49" s="4" t="n">
-        <v>12.44</v>
+        <v>52.59</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>12.4416666666667</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="M49" s="4" t="n">
-        <v>9.375</v>
+        <v>48.905</v>
       </c>
       <c r="N49" s="5">
         <f>K49/L49-1</f>
@@ -3454,25 +3454,25 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>102352</t>
+          <t>712291</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>256161</v>
+        <v>588721</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>7898074614178</t>
+          <t>7891045031257</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>MONURIL C/1 ENVELOPES 8G</t>
+          <t>NESTLE MATERNA C/30 COMPRIMIDOS</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>MONURIL 5,631G GRAN ENV 8G</t>
+          <t>NESTLE MATERNA FR 30 COMP</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
@@ -3485,20 +3485,20 @@
         <v>1</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>52.59</v>
+        <v>52.41</v>
       </c>
       <c r="J50" s="4">
         <f>G50*I50</f>
         <v/>
       </c>
       <c r="K50" s="4" t="n">
-        <v>52.59</v>
+        <v>52.41</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>69.98999999999999</v>
+        <v>58.1583333333333</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>48.905</v>
+        <v>50.575</v>
       </c>
       <c r="N50" s="5">
         <f>K50/L50-1</f>
@@ -3514,51 +3514,51 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>712291</t>
+          <t>102512</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>588721</v>
+        <v>588801</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>7891045031257</t>
+          <t>7898581710578</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>NESTLE MATERNA C/30 COMPRIMIDOS</t>
+          <t>NORIPURUM XAROPE 120ML</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>NESTLE MATERNA FR 30 COMP</t>
+          <t>NORIPURUM 10MG/ML XPE FR 120ML</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>52.41</v>
+        <v>26.06</v>
       </c>
       <c r="J51" s="4">
         <f>G51*I51</f>
         <v/>
       </c>
       <c r="K51" s="4" t="n">
-        <v>52.41</v>
+        <v>26.06</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>58.1583333333333</v>
+        <v>26.06</v>
       </c>
       <c r="M51" s="4" t="n">
-        <v>50.575</v>
+        <v>26.06</v>
       </c>
       <c r="N51" s="5">
         <f>K51/L51-1</f>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="O51" s="6" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>OK (≤ menor hist.)</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr"/>
@@ -3574,51 +3574,51 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>102512</t>
+          <t>722004</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>588801</v>
+        <v>627711</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>7898581710578</t>
+          <t>7896023799983</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>NORIPURUM XAROPE 120ML</t>
+          <t>OMEGA 3 1000MG C/60 CAPSULAS</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>NORIPURUM 10MG/ML XPE FR 120ML</t>
+          <t>OMEGA 3 1000MG 60CAP</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>26.06</v>
+        <v>19.03</v>
       </c>
       <c r="J52" s="4">
         <f>G52*I52</f>
         <v/>
       </c>
       <c r="K52" s="4" t="n">
-        <v>26.06</v>
+        <v>19.03</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>26.06</v>
+        <v>32.02</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>26.06</v>
+        <v>27.07</v>
       </c>
       <c r="N52" s="5">
         <f>K52/L52-1</f>
@@ -3634,59 +3634,59 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>722004</t>
+          <t>405453</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>627711</v>
+        <v>626351</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>7896023799983</t>
+          <t>7891158106453</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>OMEGA 3 1000MG C/60 CAPSULAS</t>
+          <t>REPOSITOR HIDROELETROLITICO COM ZINCO MORANGO PEDIALYTE MAX GARRAFA 500ML SOLUÇAO ORAL ESTERIL</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>OMEGA 3 1000MG 60CAP</t>
+          <t>PEDIALYTE MAX SOL OR FR 500ML SB MORANGO</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>19.03</v>
+        <v>21.92</v>
       </c>
       <c r="J53" s="4">
         <f>G53*I53</f>
         <v/>
       </c>
       <c r="K53" s="4" t="n">
-        <v>19.03</v>
+        <v>21.92</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>32.02</v>
+        <v>17.865</v>
       </c>
       <c r="M53" s="4" t="n">
-        <v>27.07</v>
+        <v>17.8633</v>
       </c>
       <c r="N53" s="5">
         <f>K53/L53-1</f>
         <v/>
       </c>
-      <c r="O53" s="6" t="inlineStr">
-        <is>
-          <t>OK (≤ menor hist.)</t>
+      <c r="O53" s="7" t="inlineStr">
+        <is>
+          <t>ACIMA +22.7% (vs últ. compra)</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr"/>
@@ -3694,59 +3694,59 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>405453</t>
+          <t>405381</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>626351</v>
+        <v>644221</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>7891158106453</t>
+          <t>7898636193622</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>REPOSITOR HIDROELETROLITICO COM ZINCO MORANGO PEDIALYTE MAX GARRAFA 500ML SOLUÇAO ORAL ESTERIL</t>
+          <t>PROCTAN POMADA 25G COM 10 PROTETORES HIGIENICOS PARA DEDOS</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>PEDIALYTE MAX SOL OR FR 500ML SB MORANGO</t>
+          <t>PROCTAN 25G C/ 10 LUVAS-OUTROS</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>21.92</v>
+        <v>41.77</v>
       </c>
       <c r="J54" s="4">
         <f>G54*I54</f>
         <v/>
       </c>
       <c r="K54" s="4" t="n">
-        <v>21.92</v>
+        <v>41.77</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>17.865</v>
+        <v>44.71</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>17.8633</v>
+        <v>34.175</v>
       </c>
       <c r="N54" s="5">
         <f>K54/L54-1</f>
         <v/>
       </c>
-      <c r="O54" s="7" t="inlineStr">
-        <is>
-          <t>ACIMA +22.7% (vs últ. compra)</t>
+      <c r="O54" s="6" t="inlineStr">
+        <is>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr"/>
@@ -3754,25 +3754,25 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>405381</t>
+          <t>402424</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>644221</v>
+        <v>543021</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>7898636193622</t>
+          <t>7898949409465</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>PROCTAN POMADA 25G COM 10 PROTETORES HIGIENICOS PARA DEDOS</t>
+          <t>PROCTAN HEMORROIDAS 25G</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>PROCTAN 25G C/ 10 LUVAS-OUTROS</t>
+          <t>PROCTAN 25G POMADA GENO %DN:0.00</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
@@ -3795,18 +3795,18 @@
         <v>41.77</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>44.71</v>
+        <v>41.765</v>
       </c>
       <c r="M55" s="4" t="n">
-        <v>34.175</v>
+        <v>34.1775</v>
       </c>
       <c r="N55" s="5">
         <f>K55/L55-1</f>
         <v/>
       </c>
-      <c r="O55" s="6" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
+      <c r="O55" s="7" t="inlineStr">
+        <is>
+          <t>ACIMA +0.0% (vs últ. compra)</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr"/>
@@ -3814,111 +3814,115 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>402424</t>
+          <t>102905</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>543021</v>
+        <v>96361</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>7898949409465</t>
+          <t>7896070601871</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>PROCTAN HEMORROIDAS 25G</t>
+          <t>PROFENID LIOFILIZADO FRASCO 100MG C/6 AMPOLAS</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>PROCTAN 25G POMADA GENO %DN:0.00</t>
+          <t>PROFENID 50MG SOL INJ CX 6 AMP X 2ML</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G56" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>41.77</v>
+        <v>31.85</v>
       </c>
       <c r="J56" s="4">
         <f>G56*I56</f>
         <v/>
       </c>
       <c r="K56" s="4" t="n">
-        <v>41.77</v>
+        <v>5.308333333333334</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>41.765</v>
+        <v>5.30833333333333</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>34.1775</v>
+        <v>5.0654</v>
       </c>
       <c r="N56" s="5">
         <f>K56/L56-1</f>
         <v/>
       </c>
-      <c r="O56" s="7" t="inlineStr">
-        <is>
-          <t>ACIMA +0.0% (vs últ. compra)</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="inlineStr"/>
+      <c r="O56" s="6" t="inlineStr">
+        <is>
+          <t>OK (≤ últ. compra)</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>conferir emb. (caixa c/ 6)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>102905</t>
+          <t>717046</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>96361</v>
+        <v>556761</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>7896070601871</t>
+          <t>7891010250997</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>PROFENID LIOFILIZADO FRASCO 100MG C/6 AMPOLAS</t>
+          <t>PROTETOR SOLAR NEUTROGENA SUN FRESH FACIAL FPS70 40G</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>PROFENID 50MG SOL INJ CX 6 AMP X 2ML</t>
+          <t>PROTETOR SOLAR FACIAL FPS 70 NEUTROGENA SUN FRESH BISNAGA 40G</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>31.85</v>
+        <v>49.16</v>
       </c>
       <c r="J57" s="4">
         <f>G57*I57</f>
         <v/>
       </c>
       <c r="K57" s="4" t="n">
-        <v>5.308333333333334</v>
+        <v>49.16</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>5.30833333333333</v>
+        <v>53.95</v>
       </c>
       <c r="M57" s="4" t="n">
-        <v>5.0654</v>
+        <v>47.9967</v>
       </c>
       <c r="N57" s="5">
         <f>K57/L57-1</f>
@@ -3929,60 +3933,56 @@
           <t>OK (≤ últ. compra)</t>
         </is>
       </c>
-      <c r="P57" s="2" t="inlineStr">
-        <is>
-          <t>conferir emb. (caixa c/ 6)</t>
-        </is>
-      </c>
+      <c r="P57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>717046</t>
+          <t>102953</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>556761</v>
+        <v>69321</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>7891010250997</t>
+          <t>7896206402013</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>PROTETOR SOLAR NEUTROGENA SUN FRESH FACIAL FPS70 40G</t>
+          <t>PULMICORT SUSPENSAO NEBULIZADORA 0,25MG 2ML C/5 FRASCOS</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>PROTETOR SOLAR FACIAL FPS 70 NEUTROGENA SUN FRESH BISNAGA 40G</t>
+          <t>PULMICORT 0,25MG SUS NEB CX 5 FR X 2ML</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>49.16</v>
+        <v>41.06</v>
       </c>
       <c r="J58" s="4">
         <f>G58*I58</f>
         <v/>
       </c>
       <c r="K58" s="4" t="n">
-        <v>49.16</v>
+        <v>41.06</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>53.95</v>
+        <v>41.0625</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>47.9967</v>
+        <v>39.12</v>
       </c>
       <c r="N58" s="5">
         <f>K58/L58-1</f>
@@ -3998,51 +3998,51 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>719060</t>
+          <t>102958</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>612491</v>
+        <v>500261</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>7896658037061</t>
+          <t>7897595901033</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>PROVANCE MINI 360MG C/5 SACHES</t>
+          <t>PURAN T4 100MCG C/30 COMPRIMIDOS</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>PROVANCE MINI CX 5 SACHES</t>
+          <t>PURAN T4 100MCG CX 30 COMP</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>28.52</v>
+        <v>12.28</v>
       </c>
       <c r="J59" s="4">
         <f>G59*I59</f>
         <v/>
       </c>
       <c r="K59" s="4" t="n">
-        <v>28.52</v>
+        <v>12.28</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>30.21</v>
+        <v>12.286</v>
       </c>
       <c r="M59" s="4" t="n">
-        <v>27.33</v>
+        <v>10.43</v>
       </c>
       <c r="N59" s="5">
         <f>K59/L59-1</f>
@@ -4058,59 +4058,59 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>102953</t>
+          <t>106525</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>69321</v>
+        <v>319641</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>7896206402013</t>
+          <t>7891058003562</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>PULMICORT SUSPENSAO NEBULIZADORA 0,25MG 2ML C/5 FRASCOS</t>
+          <t>PURAN T4 37,5MCG C/2X15 COMPRIMIDOS REV</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>PULMICORT 0,25MG SUS NEB CX 5 FR X 2ML</t>
+          <t>PURAN T4 37,5MCG CX 30 COMP</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>41.06</v>
+        <v>8.26</v>
       </c>
       <c r="J60" s="4">
         <f>G60*I60</f>
         <v/>
       </c>
       <c r="K60" s="4" t="n">
-        <v>41.06</v>
+        <v>8.26</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>41.0625</v>
+        <v>8.255000000000001</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>39.12</v>
+        <v>7.6</v>
       </c>
       <c r="N60" s="5">
         <f>K60/L60-1</f>
         <v/>
       </c>
-      <c r="O60" s="6" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
+      <c r="O60" s="7" t="inlineStr">
+        <is>
+          <t>ACIMA +0.1% (vs últ. compra)</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr"/>
@@ -4118,51 +4118,51 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>102958</t>
+          <t>106526</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>500261</v>
+        <v>500621</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>7897595901033</t>
+          <t>7891058003579</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>PURAN T4 100MCG C/30 COMPRIMIDOS</t>
+          <t>PURAN T4 62,5MCG C/2X15 COMPRIMIDOS REV</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>PURAN T4 100MCG CX 30 COMP</t>
+          <t>PURAN T4 62,5MCG CX 30 COMP</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>12.28</v>
+        <v>13.74</v>
       </c>
       <c r="J61" s="4">
         <f>G61*I61</f>
         <v/>
       </c>
       <c r="K61" s="4" t="n">
-        <v>12.28</v>
+        <v>13.74</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>12.286</v>
+        <v>13.74</v>
       </c>
       <c r="M61" s="4" t="n">
-        <v>10.43</v>
+        <v>12.655</v>
       </c>
       <c r="N61" s="5">
         <f>K61/L61-1</f>
@@ -4178,51 +4178,51 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>106525</t>
+          <t>718404</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>319641</v>
+        <v>578761</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>7891058003562</t>
+          <t>7898639690418</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>PURAN T4 37,5MCG C/2X15 COMPRIMIDOS REV</t>
+          <t>TERMOMETRO DIGITAL G-TECH CLINICO BRANCO C/SELO</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>PURAN T4 37,5MCG CX 30 COMP</t>
+          <t>PVV - TERMOMETRO DIGITAL CLINICO TH1027</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>8.26</v>
+        <v>9.5</v>
       </c>
       <c r="J62" s="4">
         <f>G62*I62</f>
         <v/>
       </c>
       <c r="K62" s="4" t="n">
-        <v>8.26</v>
+        <v>9.5</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>8.255000000000001</v>
+        <v>8.082000000000001</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>7.6</v>
+        <v>8.08</v>
       </c>
       <c r="N62" s="5">
         <f>K62/L62-1</f>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="O62" s="7" t="inlineStr">
         <is>
-          <t>ACIMA +0.1% (vs últ. compra)</t>
+          <t>ACIMA +17.5% (vs últ. compra)</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr"/>
@@ -4238,59 +4238,59 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>106526</t>
+          <t>401104</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>500621</v>
+        <v>14601</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>7891058003579</t>
+          <t>7891106006286</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>PURAN T4 62,5MCG C/2X15 COMPRIMIDOS REV</t>
+          <t>REDOXON GOTAS 20ML</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>PURAN T4 62,5MCG CX 30 COMP</t>
+          <t>REDOXON 200MG/ML SOL ORAL FR GTS 20ML</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>13.74</v>
+        <v>17.11</v>
       </c>
       <c r="J63" s="4">
         <f>G63*I63</f>
         <v/>
       </c>
       <c r="K63" s="4" t="n">
-        <v>13.74</v>
+        <v>17.11</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>13.74</v>
+        <v>17.1093333333333</v>
       </c>
       <c r="M63" s="4" t="n">
-        <v>12.655</v>
+        <v>13.572</v>
       </c>
       <c r="N63" s="5">
         <f>K63/L63-1</f>
         <v/>
       </c>
-      <c r="O63" s="6" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
+      <c r="O63" s="7" t="inlineStr">
+        <is>
+          <t>ACIMA +0.0% (vs últ. compra)</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr"/>
@@ -4298,59 +4298,59 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>718404</t>
+          <t>715228</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>578761</v>
+        <v>565941</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>7898639690418</t>
+          <t>7891106912655</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>TERMOMETRO DIGITAL G-TECH CLINICO BRANCO C/SELO</t>
+          <t>REDOXON TRIPLA ACAO C/10 COMPRIMIDOS EFERVESCENTES</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>PVV - TERMOMETRO DIGITAL CLINICO TH1027</t>
+          <t>REDOXON TRIPLA ACAO 10CP EFERV</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>9.5</v>
+        <v>13.55</v>
       </c>
       <c r="J64" s="4">
         <f>G64*I64</f>
         <v/>
       </c>
       <c r="K64" s="4" t="n">
-        <v>9.5</v>
+        <v>13.55</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>8.082000000000001</v>
+        <v>14.155</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>8.08</v>
+        <v>11.2925</v>
       </c>
       <c r="N64" s="5">
         <f>K64/L64-1</f>
         <v/>
       </c>
-      <c r="O64" s="7" t="inlineStr">
-        <is>
-          <t>ACIMA +17.5% (vs últ. compra)</t>
+      <c r="O64" s="6" t="inlineStr">
+        <is>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr"/>
@@ -4358,59 +4358,59 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>401104</t>
+          <t>708802</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>14601</v>
+        <v>647811</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>7891106006286</t>
+          <t>7896046390020</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>REDOXON GOTAS 20ML</t>
+          <t>RENU FRESH SOLUCAO 60ML</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>REDOXON 200MG/ML SOL ORAL FR GTS 20ML</t>
+          <t>RENU FRESH SOLUCAO 60ML-DEMAIS PROD</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>17.11</v>
+        <v>20.52</v>
       </c>
       <c r="J65" s="4">
         <f>G65*I65</f>
         <v/>
       </c>
       <c r="K65" s="4" t="n">
-        <v>17.11</v>
+        <v>20.52</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>17.1093333333333</v>
+        <v>22.2</v>
       </c>
       <c r="M65" s="4" t="n">
-        <v>13.572</v>
+        <v>19.3111</v>
       </c>
       <c r="N65" s="5">
         <f>K65/L65-1</f>
         <v/>
       </c>
-      <c r="O65" s="7" t="inlineStr">
-        <is>
-          <t>ACIMA +0.0% (vs últ. compra)</t>
+      <c r="O65" s="6" t="inlineStr">
+        <is>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr"/>
@@ -4418,51 +4418,51 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>715228</t>
+          <t>703913</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>565941</v>
+        <v>104</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>7891106912655</t>
+          <t>4005808189342</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>REDOXON TRIPLA ACAO C/10 COMPRIMIDOS EFERVESCENTES</t>
+          <t>SABONETE GEL FACIAL NIVEA EQUILIBRIO NUTRITIVO BISNAGA 150ML</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>REDOXON TRIPLA ACAO 10CP EFERV</t>
+          <t>SABONETE FACIAL GEL NIVEA EQUI NUT 150G</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>13.55</v>
+        <v>22.03</v>
       </c>
       <c r="J66" s="4">
         <f>G66*I66</f>
         <v/>
       </c>
       <c r="K66" s="4" t="n">
-        <v>13.55</v>
+        <v>22.03</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>14.155</v>
+        <v>26.19</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>11.2925</v>
+        <v>20.55</v>
       </c>
       <c r="N66" s="5">
         <f>K66/L66-1</f>
@@ -4478,59 +4478,59 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>708802</t>
+          <t>705262</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>647811</v>
+        <v>535801</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>7896046390020</t>
+          <t>7896004790633</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>RENU FRESH SOLUCAO 60ML</t>
+          <t>DERMACYD FEMINA 200ML</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>RENU FRESH SOLUCAO 60ML-DEMAIS PROD</t>
+          <t>SABONETE LIQUIDO DERMACYD FEMINA FLORAL 200 ML</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>20.52</v>
+        <v>19.95</v>
       </c>
       <c r="J67" s="4">
         <f>G67*I67</f>
         <v/>
       </c>
       <c r="K67" s="4" t="n">
-        <v>20.52</v>
+        <v>19.95</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>22.2</v>
+        <v>18.92</v>
       </c>
       <c r="M67" s="4" t="n">
-        <v>19.3111</v>
+        <v>18.61</v>
       </c>
       <c r="N67" s="5">
         <f>K67/L67-1</f>
         <v/>
       </c>
-      <c r="O67" s="6" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
+      <c r="O67" s="7" t="inlineStr">
+        <is>
+          <t>ACIMA +5.4% (vs últ. compra)</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr"/>
@@ -4538,25 +4538,25 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>703913</t>
+          <t>401161</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>104</v>
+        <v>431321</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>4005808189342</t>
+          <t>7896227800041</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>SABONETE GEL FACIAL NIVEA EQUILIBRIO NUTRITIVO BISNAGA 150ML</t>
+          <t>SALONPAS AEROSOL 80ML</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>SABONETE FACIAL GEL NIVEA EQUI NUT 150G</t>
+          <t>SALONPAS 30+38,5+38,5+19MG/ML LATA COM 80ML</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
@@ -4569,20 +4569,20 @@
         <v>1</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>22.03</v>
+        <v>37.67</v>
       </c>
       <c r="J68" s="4">
         <f>G68*I68</f>
         <v/>
       </c>
       <c r="K68" s="4" t="n">
-        <v>22.03</v>
+        <v>37.67</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>26.19</v>
+        <v>37.6733333333333</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>20.55</v>
+        <v>32.5533</v>
       </c>
       <c r="N68" s="5">
         <f>K68/L68-1</f>
@@ -4598,59 +4598,59 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>705262</t>
+          <t>401177</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>535801</v>
+        <v>244781</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>7896004790633</t>
+          <t>7898074618183</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>DERMACYD FEMINA 200ML</t>
+          <t>XAROPE SEKI 120ML</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>SABONETE LIQUIDO DERMACYD FEMINA FLORAL 200 ML</t>
+          <t>SEKI 3,54MG/ML XPE FR 120ML+CM</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>19.95</v>
+        <v>25.11</v>
       </c>
       <c r="J69" s="4">
         <f>G69*I69</f>
         <v/>
       </c>
       <c r="K69" s="4" t="n">
-        <v>19.95</v>
+        <v>25.11</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>18.92</v>
+        <v>25.11</v>
       </c>
       <c r="M69" s="4" t="n">
-        <v>18.61</v>
+        <v>18.6354</v>
       </c>
       <c r="N69" s="5">
         <f>K69/L69-1</f>
         <v/>
       </c>
-      <c r="O69" s="7" t="inlineStr">
-        <is>
-          <t>ACIMA +5.4% (vs últ. compra)</t>
+      <c r="O69" s="6" t="inlineStr">
+        <is>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr"/>
@@ -4658,51 +4658,51 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>401161</t>
+          <t>405203</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>431321</v>
+        <v>605291</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>7896227800041</t>
+          <t>7897460401934</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>SALONPAS AEROSOL 80ML</t>
+          <t>SILIMALON 70MG CAIXA 10 COMPRIMIDOS REVESTIDOS</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>SALONPAS 30+38,5+38,5+19MG/ML LATA COM 80ML</t>
+          <t>SILIMALON 100+70MG CX 10 COMP REV</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>37.67</v>
+        <v>18.34</v>
       </c>
       <c r="J70" s="4">
         <f>G70*I70</f>
         <v/>
       </c>
       <c r="K70" s="4" t="n">
-        <v>37.67</v>
+        <v>18.34</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>37.6733333333333</v>
+        <v>19.2466666666667</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>32.5533</v>
+        <v>15.4333</v>
       </c>
       <c r="N70" s="5">
         <f>K70/L70-1</f>
@@ -4718,59 +4718,59 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>401177</t>
+          <t>404725</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>244781</v>
+        <v>433941</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>7898074618183</t>
+          <t>7897460401422</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>XAROPE SEKI 120ML</t>
+          <t>SILIMALON 100MG + 70MG C/30 DRAGEAS</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>SEKI 3,54MG/ML XPE FR 120ML+CM</t>
+          <t>SILIMALON 100+70MG CX 30 DRG</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>25.11</v>
+        <v>57.79</v>
       </c>
       <c r="J71" s="4">
         <f>G71*I71</f>
         <v/>
       </c>
       <c r="K71" s="4" t="n">
-        <v>25.11</v>
+        <v>57.79</v>
       </c>
       <c r="L71" s="4" t="n">
-        <v>25.11</v>
+        <v>57.7866666666667</v>
       </c>
       <c r="M71" s="4" t="n">
-        <v>18.6354</v>
+        <v>51.28</v>
       </c>
       <c r="N71" s="5">
         <f>K71/L71-1</f>
         <v/>
       </c>
-      <c r="O71" s="6" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
+      <c r="O71" s="7" t="inlineStr">
+        <is>
+          <t>ACIMA +0.0% (vs últ. compra)</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr"/>
@@ -4778,51 +4778,51 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>405203</t>
+          <t>111035</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>605291</v>
+        <v>434001</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>7897460401934</t>
+          <t>7897460401743</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>SILIMALON 70MG CAIXA 10 COMPRIMIDOS REVESTIDOS</t>
+          <t>SILIMALON 140 100 + 140MG C/30 COMPRIMIDOS</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>SILIMALON 100+70MG CX 10 COMP REV</t>
+          <t>SILIMALON 140 140+100MG CX 30 COMP REV</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>18.34</v>
+        <v>92.47</v>
       </c>
       <c r="J72" s="4">
         <f>G72*I72</f>
         <v/>
       </c>
       <c r="K72" s="4" t="n">
-        <v>18.34</v>
+        <v>92.47</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>19.2466666666667</v>
+        <v>92.47</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>15.4333</v>
+        <v>84.03</v>
       </c>
       <c r="N72" s="5">
         <f>K72/L72-1</f>
@@ -4838,25 +4838,25 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>404725</t>
+          <t>707905</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>433941</v>
+        <v>632761</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>7897460401422</t>
+          <t>7500435171106</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>SILIMALON 100MG + 70MG C/30 DRAGEAS</t>
+          <t>TESTE CLEARBLUE GRAVIDEZ PLUS</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>SILIMALON 100+70MG CX 30 DRG</t>
+          <t>TESTE DE GRAVIDEZ CLEARBLUE PLUS-DEMAIS PROD</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
@@ -4869,28 +4869,28 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>57.79</v>
+        <v>14.49</v>
       </c>
       <c r="J73" s="4">
         <f>G73*I73</f>
         <v/>
       </c>
       <c r="K73" s="4" t="n">
-        <v>57.79</v>
+        <v>14.49</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>57.7866666666667</v>
+        <v>15.1625</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>51.28</v>
+        <v>13.3871</v>
       </c>
       <c r="N73" s="5">
         <f>K73/L73-1</f>
         <v/>
       </c>
-      <c r="O73" s="7" t="inlineStr">
-        <is>
-          <t>ACIMA +0.0% (vs últ. compra)</t>
+      <c r="O73" s="6" t="inlineStr">
+        <is>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr"/>
@@ -4898,51 +4898,51 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>111035</t>
+          <t>718105</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>434001</v>
+        <v>622921</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>7897460401743</t>
+          <t>7500435137959</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>SILIMALON 140 100 + 140MG C/30 COMPRIMIDOS</t>
+          <t>TESTE CLEARBLUE GRAVIDEZ SAIBA ANTES</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>SILIMALON 140 140+100MG CX 30 COMP REV</t>
+          <t>TESTE GRAV CLEARBLUE SAIBA ANTES-DEMAIS PROD</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>92.47</v>
+        <v>20.95</v>
       </c>
       <c r="J74" s="4">
         <f>G74*I74</f>
         <v/>
       </c>
       <c r="K74" s="4" t="n">
-        <v>92.47</v>
+        <v>20.95</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>92.47</v>
+        <v>21.65</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>84.03</v>
+        <v>19.62</v>
       </c>
       <c r="N74" s="5">
         <f>K74/L74-1</f>
@@ -4958,51 +4958,51 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>707905</t>
+          <t>103511</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>632761</v>
+        <v>416441</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>7500435171106</t>
+          <t>7898906376410</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>TESTE CLEARBLUE GRAVIDEZ PLUS</t>
+          <t>TIORFAN 100MG C/9 CAPSULAS</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>TESTE DE GRAVIDEZ CLEARBLUE PLUS-DEMAIS PROD</t>
+          <t>TIORFAN 100MG CX 9 CAP</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>14.49</v>
+        <v>42.4</v>
       </c>
       <c r="J75" s="4">
         <f>G75*I75</f>
         <v/>
       </c>
       <c r="K75" s="4" t="n">
-        <v>14.49</v>
+        <v>42.4</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>15.1625</v>
+        <v>42.4033333333333</v>
       </c>
       <c r="M75" s="4" t="n">
-        <v>13.3871</v>
+        <v>38.6471</v>
       </c>
       <c r="N75" s="5">
         <f>K75/L75-1</f>
@@ -5018,51 +5018,51 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>718105</t>
+          <t>713042</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>622921</v>
+        <v>3153</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>7500435137959</t>
+          <t>7898301056757</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>TESTE CLEARBLUE GRAVIDEZ SAIBA ANTES</t>
+          <t>TIRAS G-TECH FREE1 TESTE C/25</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>TESTE GRAV CLEARBLUE SAIBA ANTES-DEMAIS PROD</t>
+          <t>TIRA DE TESTE DE GLICOSE C/25 UND FREE 1</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>20.95</v>
+        <v>39.88</v>
       </c>
       <c r="J76" s="4">
         <f>G76*I76</f>
         <v/>
       </c>
       <c r="K76" s="4" t="n">
-        <v>20.95</v>
+        <v>39.88</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>21.65</v>
+        <v>46.42</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>19.62</v>
+        <v>43.95</v>
       </c>
       <c r="N76" s="5">
         <f>K76/L76-1</f>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="O76" s="6" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>OK (≤ menor hist.)</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr"/>
@@ -5078,59 +5078,59 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>103511</t>
+          <t>713043</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>416441</v>
+        <v>3163</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>7898906376410</t>
+          <t>7898301056740</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>TIORFAN 100MG C/9 CAPSULAS</t>
+          <t>TIRAS G-TECH FREE1 TESTE C/50</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>TIORFAN 100MG CX 9 CAP</t>
+          <t>TIRA DE TESTE DE GLICOSE C/50 UND FREE 1</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>42.4</v>
+        <v>52.34</v>
       </c>
       <c r="J77" s="4">
         <f>G77*I77</f>
         <v/>
       </c>
       <c r="K77" s="4" t="n">
-        <v>42.4</v>
+        <v>52.34</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>42.4033333333333</v>
+        <v>51.625</v>
       </c>
       <c r="M77" s="4" t="n">
-        <v>38.6471</v>
+        <v>48.88</v>
       </c>
       <c r="N77" s="5">
         <f>K77/L77-1</f>
         <v/>
       </c>
-      <c r="O77" s="6" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
+      <c r="O77" s="7" t="inlineStr">
+        <is>
+          <t>ACIMA +1.4% (vs últ. compra)</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr"/>
@@ -5138,51 +5138,51 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>713042</t>
+          <t>113397</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>3153</v>
+        <v>596521</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>7898301056757</t>
+          <t>7894916516006</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>TIRAS G-TECH FREE1 TESTE C/25</t>
+          <t>TORAGESIC SL 10MG C/10 COMPRIMIDOS SUBLINGUAIS</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>TIRA DE TESTE DE GLICOSE C/25 UND FREE 1</t>
+          <t>TORAGESIC 10MG PEEL OFF CX 10 COMP</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>39.88</v>
+        <v>26.08</v>
       </c>
       <c r="J78" s="4">
         <f>G78*I78</f>
         <v/>
       </c>
       <c r="K78" s="4" t="n">
-        <v>39.88</v>
+        <v>26.08</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>46.42</v>
+        <v>26.0814285714286</v>
       </c>
       <c r="M78" s="4" t="n">
-        <v>43.95</v>
+        <v>23.048</v>
       </c>
       <c r="N78" s="5">
         <f>K78/L78-1</f>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="O78" s="6" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr"/>
@@ -5198,59 +5198,59 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>713043</t>
+          <t>401300</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>3163</v>
+        <v>282781</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>7898301056740</t>
+          <t>7896255717885</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>TIRAS G-TECH FREE1 TESTE C/50</t>
+          <t>TROMBOFOB 200UI GEL 40G</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>TIRA DE TESTE DE GLICOSE C/50 UND FREE 1</t>
+          <t>TROMBOFOB 200UI GEL BG 40G</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>52.34</v>
+        <v>32.62</v>
       </c>
       <c r="J79" s="4">
         <f>G79*I79</f>
         <v/>
       </c>
       <c r="K79" s="4" t="n">
-        <v>52.34</v>
+        <v>32.62</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>51.625</v>
+        <v>32.62</v>
       </c>
       <c r="M79" s="4" t="n">
-        <v>48.88</v>
+        <v>25.57</v>
       </c>
       <c r="N79" s="5">
         <f>K79/L79-1</f>
         <v/>
       </c>
-      <c r="O79" s="7" t="inlineStr">
-        <is>
-          <t>ACIMA +1.4% (vs últ. compra)</t>
+      <c r="O79" s="6" t="inlineStr">
+        <is>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr"/>
@@ -5258,59 +5258,59 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>113397</t>
+          <t>103967</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>596521</v>
+        <v>326621</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>7894916516006</t>
+          <t>7891317425869</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>TORAGESIC SL 10MG C/10 COMPRIMIDOS SUBLINGUAIS</t>
+          <t>ZART 50MG C/30 COMPRIMIDOS</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>TORAGESIC 10MG PEEL OFF CX 10 COMP</t>
+          <t>ZART 50MG CX 30 COMP REV</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>26.08</v>
+        <v>4.93</v>
       </c>
       <c r="J80" s="4">
         <f>G80*I80</f>
         <v/>
       </c>
       <c r="K80" s="4" t="n">
-        <v>26.08</v>
+        <v>4.93</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>26.0814285714286</v>
+        <v>4.92444444444444</v>
       </c>
       <c r="M80" s="4" t="n">
-        <v>23.048</v>
+        <v>3.8667</v>
       </c>
       <c r="N80" s="5">
         <f>K80/L80-1</f>
         <v/>
       </c>
-      <c r="O80" s="6" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
+      <c r="O80" s="7" t="inlineStr">
+        <is>
+          <t>ACIMA +0.1% (vs últ. compra)</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr"/>
@@ -5318,51 +5318,51 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>401300</t>
+          <t>103966</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>282781</v>
+        <v>287141</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>7896255717885</t>
+          <t>7891317451417</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>TROMBOFOB 200UI GEL 40G</t>
+          <t>ZART H 50/12,5MG C/30 COMPRIMIDOS</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>TROMBOFOB 200UI GEL BG 40G</t>
+          <t>ZART H H 50+12,5MG CX 30 COMP REV</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>32.62</v>
+        <v>41.61</v>
       </c>
       <c r="J81" s="4">
         <f>G81*I81</f>
         <v/>
       </c>
       <c r="K81" s="4" t="n">
-        <v>32.62</v>
+        <v>41.61</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>32.62</v>
+        <v>41.61</v>
       </c>
       <c r="M81" s="4" t="n">
-        <v>25.57</v>
+        <v>36.88</v>
       </c>
       <c r="N81" s="5">
         <f>K81/L81-1</f>
@@ -5376,138 +5376,18 @@
       <c r="P81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>103967</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="n">
-        <v>326621</v>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>7891317425869</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>ZART 50MG C/30 COMPRIMIDOS</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>ZART 50MG CX 30 COMP REV</t>
-        </is>
-      </c>
-      <c r="F82" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="H82" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="I82" s="4" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="J82" s="4">
-        <f>G82*I82</f>
-        <v/>
-      </c>
-      <c r="K82" s="4" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="L82" s="4" t="n">
-        <v>4.92444444444444</v>
-      </c>
-      <c r="M82" s="4" t="n">
-        <v>3.8667</v>
-      </c>
-      <c r="N82" s="5">
-        <f>K82/L82-1</f>
-        <v/>
-      </c>
-      <c r="O82" s="7" t="inlineStr">
-        <is>
-          <t>ACIMA +0.1% (vs últ. compra)</t>
-        </is>
-      </c>
-      <c r="P82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>103966</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="n">
-        <v>287141</v>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>7891317451417</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>ZART H 50/12,5MG C/30 COMPRIMIDOS</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>ZART H H 50+12,5MG CX 30 COMP REV</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I83" s="4" t="n">
-        <v>41.61</v>
-      </c>
-      <c r="J83" s="4">
-        <f>G83*I83</f>
-        <v/>
-      </c>
-      <c r="K83" s="4" t="n">
-        <v>41.61</v>
-      </c>
-      <c r="L83" s="4" t="n">
-        <v>41.61</v>
-      </c>
-      <c r="M83" s="4" t="n">
-        <v>36.88</v>
-      </c>
-      <c r="N83" s="5">
-        <f>K83/L83-1</f>
-        <v/>
-      </c>
-      <c r="O83" s="6" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
-        </is>
-      </c>
-      <c r="P83" s="2" t="inlineStr"/>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="J82" s="9">
+        <f>SUM(J2:J81)</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="J84" s="9">
-        <f>SUM(J2:J83)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="10" t="inlineStr">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>Preços da cotação ePan de 04/09/2026. 'Menor hist. (un)' = menor entre melhores 3/6/12 meses; 'Últ. compra (un)' = compra atual. Status OK quando o preço unit. equivalente é ≤ menor histórico ou ≤ última compra. 'Qtd pedido' na base de faturamento do distribuidor (caixa ou unidade); 'Un. totais' = unidades da lista de compra.</t>
         </is>
